--- a/sourcedata/Dim_Products.xlsx
+++ b/sourcedata/Dim_Products.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CNS/Psychiatry</t>
+          <t>CNS/Neurology</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CNS/Psychiatry</t>
+          <t>CNS/Neurology</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CNS/Psychiatry</t>
+          <t>CNS/Neurology</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CNS/Psychiatry</t>
+          <t>CNS/Neurology</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
